--- a/feedback_forms/028_lash_salon_waiting_time_experience_survey--feedback_forms.xlsx
+++ b/feedback_forms/028_lash_salon_waiting_time_experience_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,8 +842,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,12 +905,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_1,_'text':_'very_poor'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 1, 'text': 'Very Poor'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_2,_'text':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 2, 'text': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_3,_'text':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 3, 'text': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_4,_'text':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 4, 'text': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_5,_'text':_'excellent'}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 5, 'text': 'Excellent'}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_1,_'text':_'very_poor'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 1, 'text': 'Very Poor'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_2,_'text':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 2, 'text': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_3,_'text':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 3, 'text': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_4,_'text':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 4, 'text': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_5,_'text':_'excellent'}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 5, 'text': 'Excellent'}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_1,_'text':_'very_poor'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 1, 'text': 'Very Poor'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_2,_'text':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 2, 'text': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_3,_'text':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 3, 'text': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_4,_'text':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 4, 'text': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_5,_'text':_'excellent'}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 5, 'text': 'Excellent'}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_1,_'text':_'very_poor'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 1, 'text': 'Very Poor'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_2,_'text':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 2, 'text': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_3,_'text':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 3, 'text': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_4,_'text':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 4, 'text': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_5,_'text':_'excellent'}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 5, 'text': 'Excellent'}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_1,_'text':_'very_poor'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 1, 'text': 'Very Poor'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_2,_'text':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 2, 'text': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_3,_'text':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 3, 'text': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_4,_'text':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 4, 'text': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_5,_'text':_'excellent'}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 5, 'text': 'Excellent'}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
